--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R16e034d075b8407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63a431dcdec148d7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63a431dcdec148d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb39e89e20b6045c5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb39e89e20b6045c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7331a42d30a4c4f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7331a42d30a4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R734ae8a051104620"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R734ae8a051104620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9b620c8805c849b2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9b620c8805c849b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R40bd1d75bd8e4e6f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R40bd1d75bd8e4e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R14636a865273402f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R14636a865273402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80cb244657324c5a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R80cb244657324c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Radac140523ce4296"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Radac140523ce4296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b000e40b71c4881"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b000e40b71c4881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ebdf6452a254e96"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ebdf6452a254e96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd891da5d0534535"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SparklinesLineGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd891da5d0534535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R79a067e9388349f4"/>
   </x:sheets>
 </x:workbook>
 </file>
